--- a/static/search_results_5.xlsx
+++ b/static/search_results_5.xlsx
@@ -491,28 +491,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-14 07:40:22</t>
+          <t>2026-07-15 08:08:57</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pharmacies</t>
+          <t>gyms</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Apotheke am Hauptbahnhof- Pharmacy International</t>
+          <t>King's Gym</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -524,395 +524,339 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>, Steindamm 2, 20099 Hamburg, Germany</t>
+          <t>, 3rd Floor, Midas Square, 323-324, opp. Bharat Petroleum, Godadara, Shakti Nagar, Surat, Gujarat 395012</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+49 40 241243</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>http://www.apothekeamhauptbahnhof.de/</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>medicine@pharmacy-international.de</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Medicine</t>
-        </is>
-      </c>
+          <t>087330 79422</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-14 07:40:22</t>
+          <t>2026-07-15 08:08:57</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pharmacies</t>
+          <t>gyms</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hauptbahnhof Apotheke Wandelhalle</t>
+          <t>Active Fitness Gym</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>, Wandelhalle Hamburg, Glockengießerwall 8-10, 20095 Hamburg, Germany</t>
+          <t>, 2nd floor, the palace, opposite Capital Square, Parvat Gam, Shakti Nagar, Surat, Gujarat 395010</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>+49 40 32527383</t>
+          <t>076001 61118</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://www.hauptbahnhofapotheke.de/</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>shop@hauptbahnhofapotheke.de</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Shop</t>
-        </is>
-      </c>
+          <t>http://probizo.kesug.com/</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-14 07:40:22</t>
+          <t>2026-07-15 08:08:57</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pharmacies</t>
+          <t>gyms</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rathaus-Apotheke</t>
+          <t>My Fitness Zone Gym</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>, Rathausmarkt 19, 20095 Hamburg, Germany</t>
+          <t>, 3rd Floor, MY FITNESS ZONE GYM, DR WORLD MALL, Aai Mata Rd, opp. SMC Community Hall, Parvat Patiya, Surat, Gujarat 395010</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+49 40 3696360</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>http://www.rathaus-apotheke.com/</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>service@rathaus-apotheke.com</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
+          <t>072268 38927</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-14 07:40:22</t>
+          <t>2026-07-15 08:08:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pharmacies</t>
+          <t>gyms</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Roth's old English Pharmacy</t>
+          <t>F z gym &amp; fitness</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>, Jungfernstieg 48, 20354 Hamburg, Germany</t>
+          <t>, Gonawala house, 1 st floor Motto mohallo, Rustampura, Surat, Gujarat 395002</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>+49 40 343906</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>http://www.alte-englische-apotheke.de/</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>info@alte-englische-apotheke.de</t>
-        </is>
-      </c>
+          <t>098799 86395</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-14 07:40:22</t>
+          <t>2026-07-15 08:08:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pharmacies</t>
+          <t>gyms</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Europa Apotheke</t>
+          <t>King's Gym</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>, Bergstraße 14, 20095 Hamburg, Germany</t>
+          <t>, 432-436, SHREE PUNJAN PLAZA, OPP DHUMBHAL FIRE STATION, Model Town Rd, beside LIMBAYAT ZONE OFFICE, Parvat Patiya, Surat, Gujarat 395010</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+49 40 32527690</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>http://www.europa-apotheke-hamburg.de/</t>
-        </is>
-      </c>
+          <t>075674 44999</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-14 07:40:22</t>
+          <t>2026-07-15 08:08:57</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pharmacies</t>
+          <t>gyms</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stresemann Apotheke</t>
+          <t>ABS Fitness Gym</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>, Bernstorffstraße 174, 22767 Altona, Germany</t>
+          <t>, Natraj, 342/2, Cinema Rd, opp. Soham Residency, Lal Darwaja, Patel Nagar, Surat, Gujarat 395008</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+49 40 43189988</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://www.myapotheke.de/</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>info@myapotheke.de</t>
-        </is>
-      </c>
+          <t>097272 55355</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14 07:40:22</t>
+          <t>2026-07-15 08:08:57</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pharmacies</t>
+          <t>gyms</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hafen-Apotheke</t>
+          <t>Xtreme Fitness Gym</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>, Ditmar-Koel-Straße 5, 20459 Hamburg, Germany</t>
+          <t>, Paiki Basement, Celebrity Homes, 3/1212 to 1214, Zampa Bazaar, Inderpura Ranawad, Salabatpura, Surat, Gujarat 395003</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+49 40 36905580</t>
+          <t>092657 85688</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>http://www.hafenapotheke-hamburg.de/</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>info@hafenapotheke-hamburg.de</t>
-        </is>
-      </c>
+          <t>https://instagram.com/xtreme_fitness53?utm_medium=copy_link</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14 07:40:22</t>
+          <t>2026-07-15 08:08:57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pharmacies</t>
+          <t>gyms</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vita Apotheke</t>
+          <t>Gymnation The Fitness Hub</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -924,24 +868,16 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>, Heußweg 37, 20255 Eimsbüttel, Germany</t>
+          <t>, 2nd floor, sheetal shopping centre, shop no, 1 to 7, Bhatar Rd, beside Turning Point Complex, IOC Colony, Subhash Nagar, Athwa, Surat, Gujarat 395001</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+49 40 409059</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>https://vita-apotheke-hh.de/?utm_gg=</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>mail@vita-apotheke-hh.de</t>
-        </is>
-      </c>
+          <t>085110 31349</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
     </row>
   </sheetData>
